--- a/ksoft/docs/records/Receipt_Cod_Observa_Enum.xlsx
+++ b/ksoft/docs/records/Receipt_Cod_Observa_Enum.xlsx
@@ -1282,13 +1282,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AEA6E22-F451-4894-963F-693A3D9AC6D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4AF7CB6-116F-49F9-A2BB-E71177BB648D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C7575C1-AC58-4830-8234-52D96B2906D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4D1973F-F1E7-4C5B-AFEC-B8DE49E1321B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87C3D129-5E12-422F-93A2-66AC7AFE1A1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D64AAC97-727D-437C-8097-43E6DEF491CF}"/>
 </file>
--- a/ksoft/docs/records/Receipt_Cod_Observa_Enum.xlsx
+++ b/ksoft/docs/records/Receipt_Cod_Observa_Enum.xlsx
@@ -1282,13 +1282,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4AF7CB6-116F-49F9-A2BB-E71177BB648D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AEA6E22-F451-4894-963F-693A3D9AC6D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4D1973F-F1E7-4C5B-AFEC-B8DE49E1321B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C7575C1-AC58-4830-8234-52D96B2906D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D64AAC97-727D-437C-8097-43E6DEF491CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87C3D129-5E12-422F-93A2-66AC7AFE1A1F}"/>
 </file>